--- a/simulation/模拟交易报表.xlsx
+++ b/simulation/模拟交易报表.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM107"/>
+  <dimension ref="A1:AM108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -21719,6 +21719,203 @@
         </is>
       </c>
       <c r="AM107" s="2" t="inlineStr">
+        <is>
+          <t>4116.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-11 07:30:00</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>4119.15</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>4/8</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>评分4/8低于阈值</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>4104.6</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>4107.01</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr">
+        <is>
+          <t>-0.83</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>EMA趋势 | BB外轨 | 结构突破 | 最佳时段</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>空头趋势但未跌破(距低点27.92)</t>
+        </is>
+      </c>
+      <c r="P108" s="2" t="inlineStr">
+        <is>
+          <t>4108.32</t>
+        </is>
+      </c>
+      <c r="Q108" s="2" t="inlineStr">
+        <is>
+          <t>11.0</t>
+        </is>
+      </c>
+      <c r="R108" s="2" t="inlineStr">
+        <is>
+          <t>4130.87</t>
+        </is>
+      </c>
+      <c r="S108" s="2" t="inlineStr">
+        <is>
+          <t>4091.23</t>
+        </is>
+      </c>
+      <c r="T108" s="2" t="inlineStr">
+        <is>
+          <t>↓空头</t>
+        </is>
+      </c>
+      <c r="U108" s="2" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W108" s="2" t="inlineStr">
+        <is>
+          <t>HA多头RSI=53.4</t>
+        </is>
+      </c>
+      <c r="X108" s="2" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="Y108" s="2" t="inlineStr">
+        <is>
+          <t>53.4</t>
+        </is>
+      </c>
+      <c r="Z108" s="2" t="inlineStr">
+        <is>
+          <t>4114.74</t>
+        </is>
+      </c>
+      <c r="AA108" s="2" t="inlineStr">
+        <is>
+          <t>4093.02</t>
+        </is>
+      </c>
+      <c r="AB108" s="2" t="inlineStr">
+        <is>
+          <t>120.3</t>
+        </is>
+      </c>
+      <c r="AC108" s="2" t="inlineStr">
+        <is>
+          <t>6.48</t>
+        </is>
+      </c>
+      <c r="AD108" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AE108" s="5" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="AF108" s="4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG108" s="2" t="inlineStr">
+        <is>
+          <t>跌破IB低(4119.84)反弹4118.24入场</t>
+        </is>
+      </c>
+      <c r="AH108" s="2" t="inlineStr">
+        <is>
+          <t>4126.23</t>
+        </is>
+      </c>
+      <c r="AI108" s="2" t="inlineStr">
+        <is>
+          <t>4119.84</t>
+        </is>
+      </c>
+      <c r="AJ108" s="2" t="inlineStr">
+        <is>
+          <t>6.39</t>
+        </is>
+      </c>
+      <c r="AK108" s="2" t="inlineStr">
+        <is>
+          <t>伦敦</t>
+        </is>
+      </c>
+      <c r="AL108" s="2" t="inlineStr">
+        <is>
+          <t>4123.67</t>
+        </is>
+      </c>
+      <c r="AM108" s="2" t="inlineStr">
         <is>
           <t>4116.65</t>
         </is>
@@ -22060,7 +22257,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-11 17:01:17</t>
+          <t>2026-07-11 17:33:19</t>
         </is>
       </c>
     </row>
